--- a/doc/TestDoc/Test Suite/TestPlanPrincipleStrategy.xlsx
+++ b/doc/TestDoc/Test Suite/TestPlanPrincipleStrategy.xlsx
@@ -20,9 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Aptos Narrow"/>
@@ -275,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -366,6 +364,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -998,7 +998,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
+      <c r="B15" s="40" t="n"/>
       <c r="C15" s="29" t="n">
         <v>20</v>
       </c>
@@ -1030,7 +1030,6 @@
     <col width="8.21875" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="13.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="34.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="8.88671875" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1136,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H14"/>
+  <dimension ref="A3:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1145,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1160,12 +1158,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="31" t="n"/>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="31" t="n"/>
-      <c r="G3" s="31" t="n"/>
-      <c r="H3" s="31" t="n"/>
+      <c r="C3" s="41" t="n"/>
+      <c r="D3" s="41" t="n"/>
+      <c r="E3" s="41" t="n"/>
+      <c r="F3" s="41" t="n"/>
+      <c r="G3" s="40" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
@@ -1178,12 +1175,11 @@
           <t>KongmingCombatStrategy</t>
         </is>
       </c>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="n"/>
-      <c r="H4" s="31" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="41" t="n"/>
+      <c r="E4" s="41" t="n"/>
+      <c r="F4" s="41" t="n"/>
+      <c r="G4" s="40" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
       <c r="A5" s="32" t="inlineStr">
@@ -1196,12 +1192,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="31" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="40" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
@@ -1212,12 +1207,11 @@
       <c r="B6" s="35" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="31" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
+      <c r="G6" s="40" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
       <c r="A7" s="32" t="inlineStr">
@@ -1230,12 +1224,11 @@
           <t>None (real object); statistical runs</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="40" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="33" t="inlineStr">
@@ -1298,7 +1291,6 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
-      <c r="H12" s="38" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
@@ -1324,11 +1316,6 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n"/>
       <c r="G13" s="33" t="n"/>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>guards a stuck override; nextInt(100) &lt; 50, KongmingCombatStrategy.java:8</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
@@ -1354,7 +1341,6 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="33" t="n"/>
       <c r="G14" s="33" t="n"/>
-      <c r="H14" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1374,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H19"/>
+  <dimension ref="A3:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1384,7 +1370,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1398,12 +1383,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="31" t="n"/>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="31" t="n"/>
-      <c r="G3" s="31" t="n"/>
-      <c r="H3" s="31" t="n"/>
+      <c r="C3" s="41" t="n"/>
+      <c r="D3" s="41" t="n"/>
+      <c r="E3" s="41" t="n"/>
+      <c r="F3" s="41" t="n"/>
+      <c r="G3" s="40" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
@@ -1416,12 +1400,11 @@
           <t>MarshalAbilityContext</t>
         </is>
       </c>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="n"/>
-      <c r="H4" s="31" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="41" t="n"/>
+      <c r="E4" s="41" t="n"/>
+      <c r="F4" s="41" t="n"/>
+      <c r="G4" s="40" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
       <c r="A5" s="32" t="inlineStr">
@@ -1434,12 +1417,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="31" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="40" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
@@ -1450,12 +1432,11 @@
       <c r="B6" s="35" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="31" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
+      <c r="G6" s="40" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
       <c r="A7" s="32" t="inlineStr">
@@ -1468,12 +1449,11 @@
           <t>None (real Player/Marshal objects)</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="40" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="33" t="inlineStr">
@@ -1536,7 +1516,6 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
-      <c r="H12" s="38" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
@@ -1562,7 +1541,6 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n"/>
       <c r="G13" s="33" t="n"/>
-      <c r="H13" s="38" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
@@ -1588,7 +1566,6 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="33" t="n"/>
       <c r="G14" s="33" t="n"/>
-      <c r="H14" s="38" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
@@ -1614,7 +1591,6 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="33" t="n"/>
       <c r="G15" s="33" t="n"/>
-      <c r="H15" s="38" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
@@ -1640,11 +1616,6 @@
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="33" t="n"/>
       <c r="G16" s="33" t="n"/>
-      <c r="H16" s="38" t="inlineStr">
-        <is>
-          <t>MarshalAbilityContext.java:14</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="33" t="inlineStr">
@@ -1670,11 +1641,6 @@
       <c r="E17" s="33" t="n"/>
       <c r="F17" s="33" t="n"/>
       <c r="G17" s="33" t="n"/>
-      <c r="H17" s="38" t="inlineStr">
-        <is>
-          <t>MarshalAbilityContext.java:13</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="33" t="inlineStr">
@@ -1700,11 +1666,6 @@
       <c r="E18" s="33" t="n"/>
       <c r="F18" s="33" t="n"/>
       <c r="G18" s="33" t="n"/>
-      <c r="H18" s="38" t="inlineStr">
-        <is>
-          <t>MarshalAbilityContext.java:18</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="33" t="inlineStr">
@@ -1730,11 +1691,6 @@
       <c r="E19" s="33" t="n"/>
       <c r="F19" s="33" t="n"/>
       <c r="G19" s="33" t="n"/>
-      <c r="H19" s="38" t="inlineStr">
-        <is>
-          <t>inherited from StandardMarshalStrategy</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1754,7 +1710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H16"/>
+  <dimension ref="A3:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1764,7 +1720,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -1778,12 +1733,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="31" t="n"/>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="31" t="n"/>
-      <c r="G3" s="31" t="n"/>
-      <c r="H3" s="31" t="n"/>
+      <c r="C3" s="41" t="n"/>
+      <c r="D3" s="41" t="n"/>
+      <c r="E3" s="41" t="n"/>
+      <c r="F3" s="41" t="n"/>
+      <c r="G3" s="40" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
@@ -1796,12 +1750,11 @@
           <t>StandardCombatStrategy</t>
         </is>
       </c>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="n"/>
-      <c r="H4" s="31" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="41" t="n"/>
+      <c r="E4" s="41" t="n"/>
+      <c r="F4" s="41" t="n"/>
+      <c r="G4" s="40" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
@@ -1814,12 +1767,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="31" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="40" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
@@ -1830,12 +1782,11 @@
       <c r="B6" s="39" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="31" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
+      <c r="G6" s="40" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
@@ -1848,12 +1799,11 @@
           <t>None (real objects built with Player.builder / Marshal.builder)</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="40" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="33" t="inlineStr">
@@ -1916,11 +1866,6 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
-      <c r="H12" s="38" t="inlineStr">
-        <is>
-          <t>StandardCombatStrategy.java:7</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
@@ -1946,7 +1891,6 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n"/>
       <c r="G13" s="33" t="n"/>
-      <c r="H13" s="38" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
@@ -1972,7 +1916,6 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="33" t="n"/>
       <c r="G14" s="33" t="n"/>
-      <c r="H14" s="38" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
@@ -1998,7 +1941,6 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="33" t="n"/>
       <c r="G15" s="33" t="n"/>
-      <c r="H15" s="38" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="33" t="inlineStr">
@@ -2024,11 +1966,6 @@
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="33" t="n"/>
       <c r="G16" s="33" t="n"/>
-      <c r="H16" s="38" t="inlineStr">
-        <is>
-          <t>StandardCombatStrategy.java:13</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2048,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H15"/>
+  <dimension ref="A3:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2058,7 +1995,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3">
@@ -2072,12 +2008,11 @@
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="31" t="n"/>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="31" t="n"/>
-      <c r="G3" s="31" t="n"/>
-      <c r="H3" s="31" t="n"/>
+      <c r="C3" s="41" t="n"/>
+      <c r="D3" s="41" t="n"/>
+      <c r="E3" s="41" t="n"/>
+      <c r="F3" s="41" t="n"/>
+      <c r="G3" s="40" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
@@ -2090,12 +2025,11 @@
           <t>CombatContext</t>
         </is>
       </c>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="n"/>
-      <c r="H4" s="31" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="41" t="n"/>
+      <c r="E4" s="41" t="n"/>
+      <c r="F4" s="41" t="n"/>
+      <c r="G4" s="40" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
@@ -2108,12 +2042,11 @@
           <t>Window 11, java version "1.8.0_503" , Junit 5</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="31" t="n"/>
+      <c r="C5" s="41" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="40" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
@@ -2124,12 +2057,11 @@
       <c r="B6" s="39" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="31" t="n"/>
-      <c r="F6" s="31" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="31" t="n"/>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="41" t="n"/>
+      <c r="G6" s="40" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="34" t="inlineStr">
@@ -2142,12 +2074,11 @@
           <t>None (real Player/Marshal objects)</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="40" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="33" t="inlineStr">
@@ -2210,11 +2141,6 @@
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="33" t="n"/>
-      <c r="H12" s="38" t="inlineStr">
-        <is>
-          <t>CombatContext.java:10,16-20</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
@@ -2240,11 +2166,6 @@
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="33" t="n"/>
       <c r="G13" s="33" t="n"/>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>CombatContext.java:17</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
@@ -2270,7 +2191,6 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="33" t="n"/>
       <c r="G14" s="33" t="n"/>
-      <c r="H14" s="38" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
@@ -2296,7 +2216,6 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="33" t="n"/>
       <c r="G15" s="33" t="n"/>
-      <c r="H15" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
